--- a/data/processed/harmonization/Major_and_trace_elements_total__Total_chromium/dois_filtering.xlsx
+++ b/data/processed/harmonization/Major_and_trace_elements_total__Total_chromium/dois_filtering.xlsx
@@ -611,7 +611,7 @@
         <v>30</v>
       </c>
       <c r="D3">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="E3" t="s">
         <v>50</v>
